--- a/Data/RemapDrafts/GanyuRemapDraft.xlsx
+++ b/Data/RemapDrafts/GanyuRemapDraft.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B0DA7D-67DD-47EC-9269-178703E8CC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B969B4D1-B123-4444-A13F-D4AA5E5A13DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" activeTab="1" xr2:uid="{69836935-E27C-4492-94AC-8902D071434B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{69836935-E27C-4492-94AC-8902D071434B}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.4 - Ganyu to GanyuTwilight" sheetId="1" r:id="rId1"/>
-    <sheet name="V4.4 - GanyuTwilight to Ganyu" sheetId="2" r:id="rId2"/>
+    <sheet name="Credits" sheetId="3" r:id="rId1"/>
+    <sheet name="V4.4 - Ganyu to GanyuTwilight" sheetId="1" r:id="rId2"/>
+    <sheet name="V4.4 - GanyuTwilight to Ganyu" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.4 - Ganyu to GanyuTwilight'!$A$1:$D$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.4 - GanyuTwilight to Ganyu'!$A$1:$D$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.4 - Ganyu to GanyuTwilight'!$A$1:$D$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V4.4 - GanyuTwilight to Ganyu'!$A$1:$D$95</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -134,13 +135,22 @@
   </si>
   <si>
     <t>GanyuTwilight's hair bang</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +161,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -174,14 +200,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -544,17 +574,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77544708-EF44-4E46-A32C-1CFC0B4C5FBF}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{E6AB5F4B-80BB-4622-8A34-C66302985067}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADB6D195-F5B4-4B1B-9F8A-291A31C44D97}">
   <dimension ref="A1:D94"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="122.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="122.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -568,7 +629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -576,7 +637,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -584,7 +645,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -592,7 +653,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -600,7 +661,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -608,7 +669,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -616,7 +677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -624,7 +685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -632,7 +693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -640,7 +701,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -648,7 +709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -656,7 +717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -664,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -672,7 +733,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -680,7 +741,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -688,7 +749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -696,7 +757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -710,7 +771,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -724,7 +785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -738,7 +799,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -749,7 +810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -763,7 +824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -774,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -782,7 +843,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -790,7 +851,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -798,7 +859,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -806,7 +867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -814,7 +875,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -822,7 +883,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -830,7 +891,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -838,7 +899,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -846,7 +907,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -854,7 +915,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -862,7 +923,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -870,7 +931,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -878,7 +939,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -886,7 +947,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -894,7 +955,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -902,7 +963,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -916,7 +977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -927,7 +988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -941,7 +1002,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -955,7 +1016,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -963,7 +1024,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -971,7 +1032,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -979,7 +1040,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -987,7 +1048,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -995,7 +1056,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1003,7 +1064,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1011,7 +1072,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1019,7 +1080,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1027,7 +1088,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1035,7 +1096,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1043,7 +1104,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1051,7 +1112,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1059,7 +1120,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1067,7 +1128,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1075,7 +1136,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1083,7 +1144,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1097,7 +1158,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1108,7 +1169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1119,7 +1180,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1130,7 +1191,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1141,7 +1202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1152,7 +1213,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1163,7 +1224,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1171,7 +1232,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1179,7 +1240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1187,7 +1248,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1201,7 +1262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1209,7 +1270,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1217,7 +1278,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1228,7 +1289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1236,7 +1297,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1244,7 +1305,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1252,7 +1313,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1266,7 +1327,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1274,7 +1335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1282,7 +1343,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1296,7 +1357,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1307,7 +1368,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1318,7 +1379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -1326,7 +1387,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -1334,7 +1395,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -1342,7 +1403,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -1353,7 +1414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -1364,7 +1425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -1372,7 +1433,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -1380,7 +1441,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -1391,7 +1452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -1402,7 +1463,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -1410,7 +1471,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -1418,7 +1479,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -1439,18 +1500,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB36D2F-4F42-4DD1-ABCB-AE25BB710B9F}">
   <dimension ref="A1:D95"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="122.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="122.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1464,7 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1472,7 +1533,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1480,7 +1541,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1488,7 +1549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1496,7 +1557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1504,7 +1565,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1515,7 +1576,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1523,7 +1584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1531,7 +1592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1539,7 +1600,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1550,7 +1611,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1558,7 +1619,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1566,7 +1627,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1574,7 +1635,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1582,7 +1643,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1593,7 +1654,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1601,7 +1662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1609,7 +1670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1617,7 +1678,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1625,7 +1686,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1633,7 +1694,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1641,7 +1702,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1649,7 +1710,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1657,7 +1718,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1665,7 +1726,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1673,7 +1734,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1681,7 +1742,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1689,7 +1750,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1697,7 +1758,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1705,7 +1766,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1713,7 +1774,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1721,7 +1782,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1729,7 +1790,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1737,7 +1798,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1745,7 +1806,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1753,7 +1814,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1761,7 +1822,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1769,7 +1830,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1777,7 +1838,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1785,7 +1846,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1793,7 +1854,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1801,7 +1862,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1809,7 +1870,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1817,7 +1878,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1825,7 +1886,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1833,7 +1894,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1841,7 +1902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1849,7 +1910,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1857,7 +1918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1865,7 +1926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1873,7 +1934,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1881,7 +1942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1889,7 +1950,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1897,7 +1958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1905,7 +1966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1913,7 +1974,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1921,7 +1982,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1929,7 +1990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1937,7 +1998,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1945,7 +2006,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1953,7 +2014,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1961,7 +2022,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1969,7 +2030,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1977,7 +2038,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1985,7 +2046,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1993,7 +2054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2001,7 +2062,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2009,7 +2070,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2017,7 +2078,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2025,7 +2086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2033,7 +2094,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2041,7 +2102,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2049,7 +2110,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2057,7 +2118,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2065,7 +2126,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2073,7 +2134,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2081,7 +2142,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2089,7 +2150,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2097,7 +2158,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2105,7 +2166,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2113,7 +2174,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2121,7 +2182,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2129,7 +2190,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2137,7 +2198,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2145,7 +2206,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2153,7 +2214,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2161,7 +2222,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2169,7 +2230,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2177,7 +2238,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -2185,7 +2246,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -2193,7 +2254,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -2201,7 +2262,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -2209,7 +2270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -2217,7 +2278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
